--- a/Datos Experimentales/Data 24029.xlsx
+++ b/Datos Experimentales/Data 24029.xlsx
@@ -1,7 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cltor\Documents\SB_Calibration_2025\Datos Experimentales\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EC58982-D17D-489C-B9D6-1B55C64570F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Antecedentes_info" sheetId="1" r:id="rId1"/>
     <sheet name="Antecedentes" sheetId="2" r:id="rId2"/>
@@ -18,6 +28,7 @@
     <sheet name="Manual Densidades" sheetId="13" r:id="rId13"/>
     <sheet name="Winegrid densidad" sheetId="14" r:id="rId14"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -987,11 +998,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1020,14 +1028,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1352,10 +1369,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B106"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1363,7 +1381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1371,7 +1389,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1379,7 +1397,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1387,7 +1405,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1395,7 +1413,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1403,7 +1421,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1411,7 +1429,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1419,7 +1437,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1427,7 +1445,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1435,7 +1453,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1443,7 +1461,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1451,7 +1469,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -1459,7 +1477,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -1467,7 +1485,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -1475,7 +1493,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -1483,7 +1501,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -1491,7 +1509,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -1499,7 +1517,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -1507,7 +1525,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -1515,7 +1533,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -1523,7 +1541,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -1531,7 +1549,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -1539,7 +1557,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -1547,7 +1565,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -1555,7 +1573,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -1563,7 +1581,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -1571,7 +1589,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -1579,7 +1597,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -1587,7 +1605,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -1595,7 +1613,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -1603,7 +1621,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -1611,7 +1629,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -1619,7 +1637,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -1627,7 +1645,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -1635,7 +1653,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -1643,7 +1661,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>41</v>
       </c>
@@ -1651,7 +1669,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -1659,7 +1677,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>43</v>
       </c>
@@ -1667,7 +1685,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -1675,7 +1693,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -1683,7 +1701,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -1691,7 +1709,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -1699,7 +1717,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>49</v>
       </c>
@@ -1707,7 +1725,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -1715,7 +1733,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>51</v>
       </c>
@@ -1723,7 +1741,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -1731,7 +1749,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>54</v>
       </c>
@@ -1739,7 +1757,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>55</v>
       </c>
@@ -1747,7 +1765,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>56</v>
       </c>
@@ -1755,7 +1773,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>57</v>
       </c>
@@ -1763,7 +1781,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>58</v>
       </c>
@@ -1771,7 +1789,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>59</v>
       </c>
@@ -1779,7 +1797,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -1787,7 +1805,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>62</v>
       </c>
@@ -1795,7 +1813,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>63</v>
       </c>
@@ -1803,7 +1821,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>64</v>
       </c>
@@ -1811,7 +1829,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>65</v>
       </c>
@@ -1819,7 +1837,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>67</v>
       </c>
@@ -1827,7 +1845,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>68</v>
       </c>
@@ -1835,7 +1853,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>69</v>
       </c>
@@ -1843,7 +1861,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>70</v>
       </c>
@@ -1851,7 +1869,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>71</v>
       </c>
@@ -1859,7 +1877,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>72</v>
       </c>
@@ -1867,7 +1885,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>73</v>
       </c>
@@ -1875,7 +1893,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>74</v>
       </c>
@@ -1883,7 +1901,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>75</v>
       </c>
@@ -1891,7 +1909,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>77</v>
       </c>
@@ -1899,7 +1917,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>79</v>
       </c>
@@ -1907,7 +1925,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>80</v>
       </c>
@@ -1915,7 +1933,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>81</v>
       </c>
@@ -1923,7 +1941,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>83</v>
       </c>
@@ -1931,7 +1949,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>84</v>
       </c>
@@ -1939,7 +1957,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>85</v>
       </c>
@@ -1947,7 +1965,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>86</v>
       </c>
@@ -1955,7 +1973,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>87</v>
       </c>
@@ -1963,7 +1981,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>88</v>
       </c>
@@ -1971,7 +1989,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>89</v>
       </c>
@@ -1979,7 +1997,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>90</v>
       </c>
@@ -1987,7 +2005,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>91</v>
       </c>
@@ -1995,7 +2013,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>92</v>
       </c>
@@ -2003,7 +2021,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>93</v>
       </c>
@@ -2011,7 +2029,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>94</v>
       </c>
@@ -2019,7 +2037,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>95</v>
       </c>
@@ -2027,7 +2045,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>96</v>
       </c>
@@ -2035,7 +2053,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>97</v>
       </c>
@@ -2043,7 +2061,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>99</v>
       </c>
@@ -2051,7 +2069,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>100</v>
       </c>
@@ -2059,7 +2077,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>101</v>
       </c>
@@ -2067,7 +2085,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>102</v>
       </c>
@@ -2075,7 +2093,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>103</v>
       </c>
@@ -2083,7 +2101,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>104</v>
       </c>
@@ -2091,7 +2109,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>105</v>
       </c>
@@ -2099,7 +2117,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>106</v>
       </c>
@@ -2107,7 +2125,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>107</v>
       </c>
@@ -2115,7 +2133,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>108</v>
       </c>
@@ -2123,7 +2141,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>109</v>
       </c>
@@ -2131,7 +2149,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>110</v>
       </c>
@@ -2139,7 +2157,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>111</v>
       </c>
@@ -2147,7 +2165,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>112</v>
       </c>
@@ -2155,7 +2173,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>113</v>
       </c>
@@ -2163,7 +2181,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>115</v>
       </c>
@@ -2171,7 +2189,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>116</v>
       </c>
@@ -2179,7 +2197,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>117</v>
       </c>
@@ -2187,7 +2205,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>118</v>
       </c>
@@ -2195,7 +2213,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>119</v>
       </c>
@@ -2204,27 +2222,31 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B106"/>
+    <ignoredError sqref="A1:B106" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>269</v>
       </c>
@@ -2245,17 +2267,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1"/>
+    <ignoredError sqref="A1:F1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>274</v>
       </c>
@@ -2266,7 +2290,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>277</v>
       </c>
@@ -2277,40 +2301,40 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>278</v>
       </c>
       <c r="B3">
-        <v>0.4708333333333333</v>
+        <v>0.47083333333333333</v>
       </c>
       <c r="C3">
         <v>19</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>279</v>
       </c>
       <c r="B4">
-        <v>0.7208333333333333</v>
+        <v>0.72083333333333333</v>
       </c>
       <c r="C4">
         <v>13.5</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>280</v>
       </c>
       <c r="B5">
-        <v>0.9708333333333333</v>
+        <v>0.97083333333333333</v>
       </c>
       <c r="C5">
         <v>13</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>281</v>
       </c>
@@ -2321,7 +2345,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>282</v>
       </c>
@@ -2332,7 +2356,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>283</v>
       </c>
@@ -2343,7 +2367,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>284</v>
       </c>
@@ -2354,414 +2378,416 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>285</v>
       </c>
       <c r="B10">
-        <v>2.220833333333333</v>
+        <v>2.2208333333333332</v>
       </c>
       <c r="C10">
         <v>18.5</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>286</v>
       </c>
       <c r="B11">
-        <v>2.470833333333333</v>
+        <v>2.4708333333333332</v>
       </c>
       <c r="C11">
         <v>18.5</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>287</v>
       </c>
       <c r="B12">
-        <v>2.720833333333333</v>
+        <v>2.7208333333333332</v>
       </c>
       <c r="C12">
         <v>19.5</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>288</v>
       </c>
       <c r="B13">
-        <v>2.970833333333333</v>
+        <v>2.9708333333333332</v>
       </c>
       <c r="C13">
         <v>19</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>288</v>
       </c>
       <c r="B14">
-        <v>2.970833333333333</v>
+        <v>2.9708333333333332</v>
       </c>
       <c r="C14">
         <v>19</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>289</v>
       </c>
       <c r="B15">
-        <v>3.220833333333333</v>
+        <v>3.2208333333333332</v>
       </c>
       <c r="C15">
         <v>18.5</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>290</v>
       </c>
       <c r="B16">
-        <v>3.470833333333333</v>
+        <v>3.4708333333333332</v>
       </c>
       <c r="C16">
         <v>18.5</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>291</v>
       </c>
       <c r="B17">
-        <v>3.720833333333333</v>
+        <v>3.7208333333333332</v>
       </c>
       <c r="C17">
         <v>20.5</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>292</v>
       </c>
       <c r="B18">
-        <v>3.970833333333333</v>
+        <v>3.9708333333333332</v>
       </c>
       <c r="C18">
         <v>18.5</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>293</v>
       </c>
       <c r="B19">
-        <v>4.220833333333333</v>
+        <v>4.2208333333333332</v>
       </c>
       <c r="C19">
         <v>20</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>294</v>
       </c>
       <c r="B20">
-        <v>4.470833333333333</v>
+        <v>4.4708333333333332</v>
       </c>
       <c r="C20">
         <v>19.5</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>295</v>
       </c>
       <c r="B21">
-        <v>4.720833333333333</v>
+        <v>4.7208333333333332</v>
       </c>
       <c r="C21">
         <v>18</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>296</v>
       </c>
       <c r="B22">
-        <v>4.970833333333333</v>
+        <v>4.9708333333333332</v>
       </c>
       <c r="C22">
         <v>19</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>297</v>
       </c>
       <c r="B23">
-        <v>5.220833333333333</v>
+        <v>5.2208333333333332</v>
       </c>
       <c r="C23">
-        <v>18.4</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>18.399999999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>298</v>
       </c>
       <c r="B24">
-        <v>5.470833333333333</v>
+        <v>5.4708333333333332</v>
       </c>
       <c r="C24">
         <v>18.5</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>299</v>
       </c>
       <c r="B25">
-        <v>5.720833333333333</v>
+        <v>5.7208333333333332</v>
       </c>
       <c r="C25">
         <v>19</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>300</v>
       </c>
       <c r="B26">
-        <v>5.970833333333333</v>
+        <v>5.9708333333333332</v>
       </c>
       <c r="C26">
         <v>19</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>301</v>
       </c>
       <c r="B27">
-        <v>6.220833333333333</v>
+        <v>6.2208333333333332</v>
       </c>
       <c r="C27">
         <v>19.3</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>301</v>
       </c>
       <c r="B28">
-        <v>6.220833333333333</v>
+        <v>6.2208333333333332</v>
       </c>
       <c r="C28">
-        <v>19.1</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>19.100000000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>302</v>
       </c>
       <c r="B29">
-        <v>6.470833333333333</v>
+        <v>6.4708333333333332</v>
       </c>
       <c r="C29">
         <v>18.2</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>302</v>
       </c>
       <c r="B30">
-        <v>6.470833333333333</v>
+        <v>6.4708333333333332</v>
       </c>
       <c r="C30">
         <v>18.8</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>303</v>
       </c>
       <c r="B31">
-        <v>6.720833333333333</v>
+        <v>6.7208333333333332</v>
       </c>
       <c r="C31">
         <v>19</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>303</v>
       </c>
       <c r="B32">
-        <v>6.720833333333333</v>
+        <v>6.7208333333333332</v>
       </c>
       <c r="C32">
         <v>19</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>304</v>
       </c>
       <c r="B33">
-        <v>6.970833333333333</v>
+        <v>6.9708333333333332</v>
       </c>
       <c r="C33">
         <v>19</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>305</v>
       </c>
       <c r="B34">
-        <v>7.220833333333333</v>
+        <v>7.2208333333333332</v>
       </c>
       <c r="C34">
         <v>18.5</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>306</v>
       </c>
       <c r="B35">
-        <v>7.470833333333333</v>
+        <v>7.4708333333333332</v>
       </c>
       <c r="C35">
         <v>19.5</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>307</v>
       </c>
       <c r="B36">
-        <v>7.720833333333333</v>
+        <v>7.7208333333333332</v>
       </c>
       <c r="C36">
-        <v>19.6</v>
-      </c>
-    </row>
-    <row r="37">
+        <v>19.600000000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>308</v>
       </c>
       <c r="B37">
-        <v>7.970833333333333</v>
+        <v>7.9708333333333332</v>
       </c>
       <c r="C37">
         <v>18.7</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>309</v>
       </c>
       <c r="B38">
-        <v>8.220833333333333</v>
+        <v>8.2208333333333332</v>
       </c>
       <c r="C38">
         <v>18.5</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>310</v>
       </c>
       <c r="B39">
-        <v>8.470833333333333</v>
+        <v>8.4708333333333332</v>
       </c>
       <c r="C39">
         <v>19</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>311</v>
       </c>
       <c r="B40">
-        <v>8.720833333333333</v>
+        <v>8.7208333333333332</v>
       </c>
       <c r="C40">
         <v>19.2</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>312</v>
       </c>
       <c r="B41">
-        <v>8.970833333333333</v>
+        <v>8.9708333333333332</v>
       </c>
       <c r="C41">
         <v>19.7</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>313</v>
       </c>
       <c r="B42">
-        <v>9.220833333333333</v>
+        <v>9.2208333333333332</v>
       </c>
       <c r="C42">
-        <v>18.4</v>
-      </c>
-    </row>
-    <row r="43">
+        <v>18.399999999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>314</v>
       </c>
       <c r="B43">
-        <v>9.470833333333333</v>
+        <v>9.4708333333333332</v>
       </c>
       <c r="C43">
         <v>18.5</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>315</v>
       </c>
       <c r="B44">
-        <v>9.720833333333333</v>
+        <v>9.7208333333333332</v>
       </c>
       <c r="C44">
-        <v>18.6</v>
-      </c>
-    </row>
-    <row r="45">
+        <v>18.600000000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>316</v>
       </c>
       <c r="B45">
-        <v>9.970833333333333</v>
+        <v>9.9708333333333332</v>
       </c>
       <c r="C45">
-        <v>18.9</v>
+        <v>18.899999999999999</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C45"/>
+    <ignoredError sqref="A1:C45" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>274</v>
       </c>
@@ -2772,7 +2798,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>277</v>
       </c>
@@ -2783,40 +2809,40 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>278</v>
       </c>
       <c r="B3">
-        <v>0.4708333333333333</v>
+        <v>0.47083333333333333</v>
       </c>
       <c r="C3">
         <v>1082</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>279</v>
       </c>
       <c r="B4">
-        <v>0.7208333333333333</v>
+        <v>0.72083333333333333</v>
       </c>
       <c r="C4">
         <v>1085</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>280</v>
       </c>
       <c r="B5">
-        <v>0.9708333333333333</v>
+        <v>0.97083333333333333</v>
       </c>
       <c r="C5">
         <v>1085</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>281</v>
       </c>
@@ -2827,7 +2853,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>282</v>
       </c>
@@ -2838,7 +2864,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>283</v>
       </c>
@@ -2849,7 +2875,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>284</v>
       </c>
@@ -2860,414 +2886,416 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>285</v>
       </c>
       <c r="B10">
-        <v>2.220833333333333</v>
+        <v>2.2208333333333332</v>
       </c>
       <c r="C10">
         <v>1048</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>286</v>
       </c>
       <c r="B11">
-        <v>2.470833333333333</v>
+        <v>2.4708333333333332</v>
       </c>
       <c r="C11">
         <v>1042</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>287</v>
       </c>
       <c r="B12">
-        <v>2.720833333333333</v>
+        <v>2.7208333333333332</v>
       </c>
       <c r="C12">
         <v>1039</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>288</v>
       </c>
       <c r="B13">
-        <v>2.970833333333333</v>
+        <v>2.9708333333333332</v>
       </c>
       <c r="C13">
         <v>1033</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>288</v>
       </c>
       <c r="B14">
-        <v>2.970833333333333</v>
+        <v>2.9708333333333332</v>
       </c>
       <c r="C14">
         <v>1033</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>289</v>
       </c>
       <c r="B15">
-        <v>3.220833333333333</v>
+        <v>3.2208333333333332</v>
       </c>
       <c r="C15">
         <v>1031</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>290</v>
       </c>
       <c r="B16">
-        <v>3.470833333333333</v>
+        <v>3.4708333333333332</v>
       </c>
       <c r="C16">
         <v>1025</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>291</v>
       </c>
       <c r="B17">
-        <v>3.720833333333333</v>
+        <v>3.7208333333333332</v>
       </c>
       <c r="C17">
         <v>1019</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>292</v>
       </c>
       <c r="B18">
-        <v>3.970833333333333</v>
+        <v>3.9708333333333332</v>
       </c>
       <c r="C18">
         <v>1018</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>293</v>
       </c>
       <c r="B19">
-        <v>4.220833333333333</v>
+        <v>4.2208333333333332</v>
       </c>
       <c r="C19">
         <v>1015</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>294</v>
       </c>
       <c r="B20">
-        <v>4.470833333333333</v>
+        <v>4.4708333333333332</v>
       </c>
       <c r="C20">
         <v>1012</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>295</v>
       </c>
       <c r="B21">
-        <v>4.720833333333333</v>
+        <v>4.7208333333333332</v>
       </c>
       <c r="C21">
         <v>1010</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>296</v>
       </c>
       <c r="B22">
-        <v>4.970833333333333</v>
+        <v>4.9708333333333332</v>
       </c>
       <c r="C22">
         <v>1007</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>297</v>
       </c>
       <c r="B23">
-        <v>5.220833333333333</v>
+        <v>5.2208333333333332</v>
       </c>
       <c r="C23">
         <v>1007</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>298</v>
       </c>
       <c r="B24">
-        <v>5.470833333333333</v>
+        <v>5.4708333333333332</v>
       </c>
       <c r="C24">
         <v>1005</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>299</v>
       </c>
       <c r="B25">
-        <v>5.720833333333333</v>
+        <v>5.7208333333333332</v>
       </c>
       <c r="C25">
         <v>1003</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>300</v>
       </c>
       <c r="B26">
-        <v>5.970833333333333</v>
+        <v>5.9708333333333332</v>
       </c>
       <c r="C26">
         <v>1001</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>301</v>
       </c>
       <c r="B27">
-        <v>6.220833333333333</v>
+        <v>6.2208333333333332</v>
       </c>
       <c r="C27">
         <v>999</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>301</v>
       </c>
       <c r="B28">
-        <v>6.220833333333333</v>
+        <v>6.2208333333333332</v>
       </c>
       <c r="C28">
         <v>1001</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>302</v>
       </c>
       <c r="B29">
-        <v>6.470833333333333</v>
+        <v>6.4708333333333332</v>
       </c>
       <c r="C29">
         <v>999</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>302</v>
       </c>
       <c r="B30">
-        <v>6.470833333333333</v>
+        <v>6.4708333333333332</v>
       </c>
       <c r="C30">
         <v>998</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>303</v>
       </c>
       <c r="B31">
-        <v>6.720833333333333</v>
+        <v>6.7208333333333332</v>
       </c>
       <c r="C31">
         <v>999</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>303</v>
       </c>
       <c r="B32">
-        <v>6.720833333333333</v>
+        <v>6.7208333333333332</v>
       </c>
       <c r="C32">
         <v>998</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>304</v>
       </c>
       <c r="B33">
-        <v>6.970833333333333</v>
+        <v>6.9708333333333332</v>
       </c>
       <c r="C33">
         <v>999</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>305</v>
       </c>
       <c r="B34">
-        <v>7.220833333333333</v>
+        <v>7.2208333333333332</v>
       </c>
       <c r="C34">
         <v>997</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>306</v>
       </c>
       <c r="B35">
-        <v>7.470833333333333</v>
+        <v>7.4708333333333332</v>
       </c>
       <c r="C35">
         <v>996</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>307</v>
       </c>
       <c r="B36">
-        <v>7.720833333333333</v>
+        <v>7.7208333333333332</v>
       </c>
       <c r="C36">
         <v>995</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>308</v>
       </c>
       <c r="B37">
-        <v>7.970833333333333</v>
+        <v>7.9708333333333332</v>
       </c>
       <c r="C37">
         <v>995</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>309</v>
       </c>
       <c r="B38">
-        <v>8.220833333333333</v>
+        <v>8.2208333333333332</v>
       </c>
       <c r="C38">
         <v>995</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>310</v>
       </c>
       <c r="B39">
-        <v>8.470833333333333</v>
+        <v>8.4708333333333332</v>
       </c>
       <c r="C39">
         <v>994</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>311</v>
       </c>
       <c r="B40">
-        <v>8.720833333333333</v>
+        <v>8.7208333333333332</v>
       </c>
       <c r="C40">
         <v>994</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>312</v>
       </c>
       <c r="B41">
-        <v>8.970833333333333</v>
+        <v>8.9708333333333332</v>
       </c>
       <c r="C41">
         <v>994</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>313</v>
       </c>
       <c r="B42">
-        <v>9.220833333333333</v>
+        <v>9.2208333333333332</v>
       </c>
       <c r="C42">
         <v>994</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>314</v>
       </c>
       <c r="B43">
-        <v>9.470833333333333</v>
+        <v>9.4708333333333332</v>
       </c>
       <c r="C43">
         <v>994</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>315</v>
       </c>
       <c r="B44">
-        <v>9.720833333333333</v>
+        <v>9.7208333333333332</v>
       </c>
       <c r="C44">
         <v>993</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>316</v>
       </c>
       <c r="B45">
-        <v>9.970833333333333</v>
+        <v>9.9708333333333332</v>
       </c>
       <c r="C45">
         <v>993</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C45"/>
+    <ignoredError sqref="A1:C45" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>274</v>
       </c>
@@ -3291,17 +3319,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
+    <ignoredError sqref="A1:G1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:CO2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:93" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -3582,7 +3612,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:93" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9848</v>
       </c>
@@ -3617,7 +3647,7 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>45373.65416666667</v>
+        <v>45373.654166666667</v>
       </c>
       <c r="M2" t="s">
         <v>124</v>
@@ -3626,7 +3656,7 @@
         <v>125</v>
       </c>
       <c r="O2">
-        <v>45380.65416666667</v>
+        <v>45380.654166666667</v>
       </c>
       <c r="P2" t="s">
         <v>126</v>
@@ -3707,7 +3737,7 @@
         <v>134</v>
       </c>
       <c r="AS2">
-        <v>18.9</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="AT2">
         <v>10.6</v>
@@ -3773,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="BO2">
-        <v>0.014</v>
+        <v>1.4E-2</v>
       </c>
       <c r="BP2">
         <v>0</v>
@@ -3815,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="CC2">
-        <v>0.048</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="CD2">
         <v>0</v>
@@ -3843,17 +3873,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:CO2"/>
+    <ignoredError sqref="A1:CO2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Q12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>142</v>
       </c>
@@ -3906,7 +3938,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9848</v>
       </c>
@@ -3935,7 +3967,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9848</v>
       </c>
@@ -3970,7 +4002,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9848</v>
       </c>
@@ -3999,7 +4031,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9848</v>
       </c>
@@ -4013,7 +4045,7 @@
         <v>167</v>
       </c>
       <c r="E5">
-        <v>0.014</v>
+        <v>1.4E-2</v>
       </c>
       <c r="F5" t="s">
         <v>163</v>
@@ -4049,7 +4081,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9848</v>
       </c>
@@ -4063,7 +4095,7 @@
         <v>167</v>
       </c>
       <c r="E6">
-        <v>0.048</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="F6" t="s">
         <v>163</v>
@@ -4099,7 +4131,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9848</v>
       </c>
@@ -4134,7 +4166,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9848</v>
       </c>
@@ -4181,7 +4213,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9848</v>
       </c>
@@ -4210,7 +4242,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9848</v>
       </c>
@@ -4245,7 +4277,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9848</v>
       </c>
@@ -4280,7 +4312,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9848</v>
       </c>
@@ -4316,17 +4348,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q12"/>
+    <ignoredError sqref="A1:Q12" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>142</v>
       </c>
@@ -4358,7 +4392,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9848</v>
       </c>
@@ -4390,7 +4424,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9848</v>
       </c>
@@ -4422,7 +4456,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9848</v>
       </c>
@@ -4455,27 +4489,31 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
+    <ignoredError sqref="A1:J4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>142</v>
       </c>
@@ -4507,7 +4545,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9848</v>
       </c>
@@ -4540,17 +4578,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J2"/>
+    <ignoredError sqref="A1:J2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>142</v>
       </c>
@@ -4567,7 +4607,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9848</v>
       </c>
@@ -4579,27 +4619,31 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+    <ignoredError sqref="A1:E2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:P36"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>142</v>
       </c>
@@ -4649,7 +4693,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9848</v>
       </c>
@@ -4662,7 +4706,7 @@
       <c r="D2">
         <v>6823</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>45373.78</v>
       </c>
       <c r="F2" t="s">
@@ -4693,13 +4737,13 @@
         <v>225</v>
       </c>
       <c r="O2">
-        <v>7.5735</v>
+        <v>7.5735000000000001</v>
       </c>
       <c r="P2" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9848</v>
       </c>
@@ -4712,7 +4756,7 @@
       <c r="D3">
         <v>6823</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>45373.78</v>
       </c>
       <c r="F3" t="s">
@@ -4743,13 +4787,13 @@
         <v>225</v>
       </c>
       <c r="O3">
-        <v>3.435</v>
+        <v>3.4350000000000001</v>
       </c>
       <c r="P3" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9848</v>
       </c>
@@ -4762,7 +4806,7 @@
       <c r="D4">
         <v>6823</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>45373.78</v>
       </c>
       <c r="F4" t="s">
@@ -4799,7 +4843,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9848</v>
       </c>
@@ -4812,7 +4856,7 @@
       <c r="D5">
         <v>6823</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>45373.78</v>
       </c>
       <c r="F5" t="s">
@@ -4849,7 +4893,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9848</v>
       </c>
@@ -4862,7 +4906,7 @@
       <c r="D6">
         <v>6823</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>45373.78</v>
       </c>
       <c r="F6" t="s">
@@ -4899,7 +4943,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9848</v>
       </c>
@@ -4912,7 +4956,7 @@
       <c r="D7">
         <v>6823</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>45373.78</v>
       </c>
       <c r="F7" t="s">
@@ -4949,7 +4993,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9848</v>
       </c>
@@ -4962,7 +5006,7 @@
       <c r="D8">
         <v>6823</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>45373.78</v>
       </c>
       <c r="F8" t="s">
@@ -4999,7 +5043,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9848</v>
       </c>
@@ -5012,8 +5056,8 @@
       <c r="D9">
         <v>6890</v>
       </c>
-      <c r="E9">
-        <v>45376.65954861111</v>
+      <c r="E9" s="1">
+        <v>45373.659548611111</v>
       </c>
       <c r="F9" t="s">
         <v>123</v>
@@ -5043,13 +5087,13 @@
         <v>225</v>
       </c>
       <c r="O9">
-        <v>7.8642</v>
+        <v>7.8642000000000003</v>
       </c>
       <c r="P9" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9848</v>
       </c>
@@ -5062,8 +5106,8 @@
       <c r="D10">
         <v>6890</v>
       </c>
-      <c r="E10">
-        <v>45376.65954861111</v>
+      <c r="E10" s="1">
+        <v>45373.659548611111</v>
       </c>
       <c r="F10" t="s">
         <v>123</v>
@@ -5099,7 +5143,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9848</v>
       </c>
@@ -5112,8 +5156,8 @@
       <c r="D11">
         <v>6890</v>
       </c>
-      <c r="E11">
-        <v>45376.65954861111</v>
+      <c r="E11" s="1">
+        <v>45373.659548611111</v>
       </c>
       <c r="F11" t="s">
         <v>123</v>
@@ -5149,7 +5193,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9848</v>
       </c>
@@ -5162,8 +5206,8 @@
       <c r="D12">
         <v>6890</v>
       </c>
-      <c r="E12">
-        <v>45376.65954861111</v>
+      <c r="E12" s="1">
+        <v>45373.659548611111</v>
       </c>
       <c r="F12" t="s">
         <v>123</v>
@@ -5199,7 +5243,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9848</v>
       </c>
@@ -5212,8 +5256,8 @@
       <c r="D13">
         <v>6890</v>
       </c>
-      <c r="E13">
-        <v>45376.65954861111</v>
+      <c r="E13" s="1">
+        <v>45373.659548611111</v>
       </c>
       <c r="F13" t="s">
         <v>123</v>
@@ -5249,7 +5293,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>9848</v>
       </c>
@@ -5262,8 +5306,8 @@
       <c r="D14">
         <v>6890</v>
       </c>
-      <c r="E14">
-        <v>45376.65954861111</v>
+      <c r="E14" s="1">
+        <v>45373.659548611111</v>
       </c>
       <c r="F14" t="s">
         <v>123</v>
@@ -5293,13 +5337,13 @@
         <v>225</v>
       </c>
       <c r="O14">
-        <v>37.7</v>
+        <v>37.700000000000003</v>
       </c>
       <c r="P14" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>9848</v>
       </c>
@@ -5312,8 +5356,8 @@
       <c r="D15">
         <v>6890</v>
       </c>
-      <c r="E15">
-        <v>45376.65954861111</v>
+      <c r="E15" s="1">
+        <v>45373.659548611111</v>
       </c>
       <c r="F15" t="s">
         <v>123</v>
@@ -5349,7 +5393,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>9848</v>
       </c>
@@ -5362,8 +5406,8 @@
       <c r="D16">
         <v>7093</v>
       </c>
-      <c r="E16">
-        <v>45383.61876157408</v>
+      <c r="E16" s="1">
+        <v>45383.618761574078</v>
       </c>
       <c r="F16" t="s">
         <v>123</v>
@@ -5399,7 +5443,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>9848</v>
       </c>
@@ -5412,7 +5456,7 @@
       <c r="D17">
         <v>7101</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="1">
         <v>45383.623877314814</v>
       </c>
       <c r="F17" t="s">
@@ -5449,7 +5493,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>9848</v>
       </c>
@@ -5462,7 +5506,7 @@
       <c r="D18">
         <v>7174</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="1">
         <v>45384.862754629634</v>
       </c>
       <c r="F18" t="s">
@@ -5499,7 +5543,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>9848</v>
       </c>
@@ -5512,7 +5556,7 @@
       <c r="D19">
         <v>7174</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="1">
         <v>45384.862754629634</v>
       </c>
       <c r="F19" t="s">
@@ -5549,7 +5593,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>9848</v>
       </c>
@@ -5562,7 +5606,7 @@
       <c r="D20">
         <v>7174</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="1">
         <v>45384.862754629634</v>
       </c>
       <c r="F20" t="s">
@@ -5599,7 +5643,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>9848</v>
       </c>
@@ -5612,7 +5656,7 @@
       <c r="D21">
         <v>7174</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="1">
         <v>45384.862754629634</v>
       </c>
       <c r="F21" t="s">
@@ -5649,7 +5693,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>9848</v>
       </c>
@@ -5662,7 +5706,7 @@
       <c r="D22">
         <v>7174</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="1">
         <v>45384.862754629634</v>
       </c>
       <c r="F22" t="s">
@@ -5693,13 +5737,13 @@
         <v>225</v>
       </c>
       <c r="O22">
-        <v>0.131</v>
+        <v>0.13100000000000001</v>
       </c>
       <c r="P22" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>9848</v>
       </c>
@@ -5712,7 +5756,7 @@
       <c r="D23">
         <v>7174</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="1">
         <v>45384.862754629634</v>
       </c>
       <c r="F23" t="s">
@@ -5743,13 +5787,13 @@
         <v>225</v>
       </c>
       <c r="O23">
-        <v>0.131</v>
+        <v>0.13100000000000001</v>
       </c>
       <c r="P23" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>9848</v>
       </c>
@@ -5762,7 +5806,7 @@
       <c r="D24">
         <v>7174</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="1">
         <v>45384.862754629634</v>
       </c>
       <c r="F24" t="s">
@@ -5799,7 +5843,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>9848</v>
       </c>
@@ -5812,7 +5856,7 @@
       <c r="D25">
         <v>7174</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="1">
         <v>45384.862754629634</v>
       </c>
       <c r="F25" t="s">
@@ -5849,7 +5893,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>9848</v>
       </c>
@@ -5862,7 +5906,7 @@
       <c r="D26">
         <v>7174</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="1">
         <v>45384.862754629634</v>
       </c>
       <c r="F26" t="s">
@@ -5899,7 +5943,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>9848</v>
       </c>
@@ -5912,8 +5956,8 @@
       <c r="D27">
         <v>7420</v>
       </c>
-      <c r="E27">
-        <v>45391.68554398148</v>
+      <c r="E27" s="1">
+        <v>45391.685543981483</v>
       </c>
       <c r="F27" t="s">
         <v>123</v>
@@ -5949,7 +5993,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>9848</v>
       </c>
@@ -5962,8 +6006,8 @@
       <c r="D28">
         <v>7420</v>
       </c>
-      <c r="E28">
-        <v>45391.68554398148</v>
+      <c r="E28" s="1">
+        <v>45391.685543981483</v>
       </c>
       <c r="F28" t="s">
         <v>123</v>
@@ -5999,7 +6043,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>9848</v>
       </c>
@@ -6012,8 +6056,8 @@
       <c r="D29">
         <v>7420</v>
       </c>
-      <c r="E29">
-        <v>45391.68554398148</v>
+      <c r="E29" s="1">
+        <v>45391.685543981483</v>
       </c>
       <c r="F29" t="s">
         <v>123</v>
@@ -6049,7 +6093,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>9848</v>
       </c>
@@ -6062,8 +6106,8 @@
       <c r="D30">
         <v>7420</v>
       </c>
-      <c r="E30">
-        <v>45391.68554398148</v>
+      <c r="E30" s="1">
+        <v>45391.685543981483</v>
       </c>
       <c r="F30" t="s">
         <v>123</v>
@@ -6099,7 +6143,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>9848</v>
       </c>
@@ -6112,8 +6156,8 @@
       <c r="D31">
         <v>7420</v>
       </c>
-      <c r="E31">
-        <v>45391.68554398148</v>
+      <c r="E31" s="1">
+        <v>45391.685543981483</v>
       </c>
       <c r="F31" t="s">
         <v>123</v>
@@ -6143,13 +6187,13 @@
         <v>225</v>
       </c>
       <c r="O31">
-        <v>0.101</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="P31" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>9848</v>
       </c>
@@ -6162,8 +6206,8 @@
       <c r="D32">
         <v>7420</v>
       </c>
-      <c r="E32">
-        <v>45391.68554398148</v>
+      <c r="E32" s="1">
+        <v>45391.685543981483</v>
       </c>
       <c r="F32" t="s">
         <v>123</v>
@@ -6199,7 +6243,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>9848</v>
       </c>
@@ -6212,8 +6256,8 @@
       <c r="D33">
         <v>7420</v>
       </c>
-      <c r="E33">
-        <v>45391.68554398148</v>
+      <c r="E33" s="1">
+        <v>45391.685543981483</v>
       </c>
       <c r="F33" t="s">
         <v>123</v>
@@ -6243,13 +6287,13 @@
         <v>225</v>
       </c>
       <c r="O33">
-        <v>0.101</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="P33" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>9848</v>
       </c>
@@ -6262,8 +6306,8 @@
       <c r="D34">
         <v>7420</v>
       </c>
-      <c r="E34">
-        <v>45391.68554398148</v>
+      <c r="E34" s="1">
+        <v>45391.685543981483</v>
       </c>
       <c r="F34" t="s">
         <v>123</v>
@@ -6299,7 +6343,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>9848</v>
       </c>
@@ -6312,8 +6356,8 @@
       <c r="D35">
         <v>7420</v>
       </c>
-      <c r="E35">
-        <v>45391.68554398148</v>
+      <c r="E35" s="1">
+        <v>45391.685543981483</v>
       </c>
       <c r="F35" t="s">
         <v>123</v>
@@ -6349,7 +6393,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>9848</v>
       </c>
@@ -6362,8 +6406,8 @@
       <c r="D36">
         <v>7420</v>
       </c>
-      <c r="E36">
-        <v>45391.68554398148</v>
+      <c r="E36" s="1">
+        <v>45391.685543981483</v>
       </c>
       <c r="F36" t="s">
         <v>123</v>
@@ -6400,8 +6444,9 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P36"/>
+    <ignoredError sqref="A1:P8 A16:P36 A9:D9 F9:P9 A10:D15 F10:P15" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Datos Experimentales/Data 24029.xlsx
+++ b/Datos Experimentales/Data 24029.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cltor\Documents\SB_Calibration_2025\Datos Experimentales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EC58982-D17D-489C-B9D6-1B55C64570F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73BA445C-69C3-4C28-9796-9FCF92704D91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="321">
   <si>
     <t>parametro</t>
   </si>
@@ -993,6 +993,9 @@
   </si>
   <si>
     <t>volumen</t>
+  </si>
+  <si>
+    <t>4. Descube</t>
   </si>
 </sst>
 </file>
@@ -1371,9 +1374,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B106"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1381,7 +1384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1389,7 +1392,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1397,7 +1400,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1405,7 +1408,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1413,7 +1416,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1421,7 +1424,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1429,7 +1432,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1437,7 +1440,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1445,7 +1448,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1453,7 +1456,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1461,7 +1464,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1469,7 +1472,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -1477,7 +1480,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -1485,7 +1488,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -1493,7 +1496,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -1501,7 +1504,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -1509,7 +1512,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -1517,7 +1520,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -1525,7 +1528,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -1533,7 +1536,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -1541,7 +1544,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -1549,7 +1552,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -1557,7 +1560,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -1565,7 +1568,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -1573,7 +1576,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -1581,7 +1584,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -1589,7 +1592,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -1597,7 +1600,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -1605,7 +1608,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -1613,7 +1616,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -1621,7 +1624,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -1629,7 +1632,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -1637,7 +1640,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -1645,7 +1648,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -1653,7 +1656,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -1661,7 +1664,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>41</v>
       </c>
@@ -1669,7 +1672,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -1677,7 +1680,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>43</v>
       </c>
@@ -1685,7 +1688,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -1693,7 +1696,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -1701,7 +1704,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -1709,7 +1712,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -1717,7 +1720,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>49</v>
       </c>
@@ -1725,7 +1728,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -1733,7 +1736,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>51</v>
       </c>
@@ -1741,7 +1744,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -1749,7 +1752,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>54</v>
       </c>
@@ -1757,7 +1760,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>55</v>
       </c>
@@ -1765,7 +1768,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>56</v>
       </c>
@@ -1773,7 +1776,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>57</v>
       </c>
@@ -1781,7 +1784,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>58</v>
       </c>
@@ -1789,7 +1792,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>59</v>
       </c>
@@ -1797,7 +1800,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -1805,7 +1808,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>62</v>
       </c>
@@ -1813,7 +1816,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>63</v>
       </c>
@@ -1821,7 +1824,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>64</v>
       </c>
@@ -1829,7 +1832,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>65</v>
       </c>
@@ -1837,7 +1840,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="59" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>67</v>
       </c>
@@ -1845,7 +1848,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>68</v>
       </c>
@@ -1853,7 +1856,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>69</v>
       </c>
@@ -1861,7 +1864,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>70</v>
       </c>
@@ -1869,7 +1872,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>71</v>
       </c>
@@ -1877,7 +1880,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>72</v>
       </c>
@@ -1885,7 +1888,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>73</v>
       </c>
@@ -1893,7 +1896,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>74</v>
       </c>
@@ -1901,7 +1904,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>75</v>
       </c>
@@ -1909,7 +1912,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>77</v>
       </c>
@@ -1917,7 +1920,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="69" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>79</v>
       </c>
@@ -1925,7 +1928,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>80</v>
       </c>
@@ -1933,7 +1936,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>81</v>
       </c>
@@ -1941,7 +1944,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="72" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>83</v>
       </c>
@@ -1949,7 +1952,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>84</v>
       </c>
@@ -1957,7 +1960,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>85</v>
       </c>
@@ -1965,7 +1968,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>86</v>
       </c>
@@ -1973,7 +1976,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>87</v>
       </c>
@@ -1981,7 +1984,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>88</v>
       </c>
@@ -1989,7 +1992,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>89</v>
       </c>
@@ -1997,7 +2000,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>90</v>
       </c>
@@ -2005,7 +2008,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>91</v>
       </c>
@@ -2013,7 +2016,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>92</v>
       </c>
@@ -2021,7 +2024,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>93</v>
       </c>
@@ -2029,7 +2032,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>94</v>
       </c>
@@ -2037,7 +2040,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>95</v>
       </c>
@@ -2045,7 +2048,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>96</v>
       </c>
@@ -2053,7 +2056,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>97</v>
       </c>
@@ -2061,7 +2064,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="87" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>99</v>
       </c>
@@ -2069,7 +2072,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>100</v>
       </c>
@@ -2077,7 +2080,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>101</v>
       </c>
@@ -2085,7 +2088,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>102</v>
       </c>
@@ -2093,7 +2096,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>103</v>
       </c>
@@ -2101,7 +2104,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>104</v>
       </c>
@@ -2109,7 +2112,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>105</v>
       </c>
@@ -2117,7 +2120,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>106</v>
       </c>
@@ -2125,7 +2128,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>107</v>
       </c>
@@ -2133,7 +2136,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>108</v>
       </c>
@@ -2141,7 +2144,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>109</v>
       </c>
@@ -2149,7 +2152,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>110</v>
       </c>
@@ -2157,7 +2160,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>111</v>
       </c>
@@ -2165,7 +2168,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>112</v>
       </c>
@@ -2173,7 +2176,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>113</v>
       </c>
@@ -2181,7 +2184,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="102" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>115</v>
       </c>
@@ -2189,7 +2192,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>116</v>
       </c>
@@ -2197,7 +2200,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>117</v>
       </c>
@@ -2205,7 +2208,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>118</v>
       </c>
@@ -2213,7 +2216,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>119</v>
       </c>
@@ -2232,7 +2235,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -2244,9 +2247,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>269</v>
       </c>
@@ -2277,9 +2280,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C45"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>274</v>
       </c>
@@ -2290,7 +2293,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>277</v>
       </c>
@@ -2301,7 +2304,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>278</v>
       </c>
@@ -2312,7 +2315,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>279</v>
       </c>
@@ -2323,7 +2326,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>280</v>
       </c>
@@ -2334,7 +2337,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>281</v>
       </c>
@@ -2345,7 +2348,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>282</v>
       </c>
@@ -2356,7 +2359,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>283</v>
       </c>
@@ -2367,7 +2370,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>284</v>
       </c>
@@ -2378,7 +2381,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>285</v>
       </c>
@@ -2389,7 +2392,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>286</v>
       </c>
@@ -2400,7 +2403,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>287</v>
       </c>
@@ -2411,7 +2414,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>288</v>
       </c>
@@ -2422,7 +2425,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>288</v>
       </c>
@@ -2433,7 +2436,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>289</v>
       </c>
@@ -2444,7 +2447,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>290</v>
       </c>
@@ -2455,7 +2458,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>291</v>
       </c>
@@ -2466,7 +2469,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>292</v>
       </c>
@@ -2477,7 +2480,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>293</v>
       </c>
@@ -2488,7 +2491,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>294</v>
       </c>
@@ -2499,7 +2502,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>295</v>
       </c>
@@ -2510,7 +2513,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>296</v>
       </c>
@@ -2521,7 +2524,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>297</v>
       </c>
@@ -2532,7 +2535,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>298</v>
       </c>
@@ -2543,7 +2546,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>299</v>
       </c>
@@ -2554,7 +2557,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>300</v>
       </c>
@@ -2565,7 +2568,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>301</v>
       </c>
@@ -2576,7 +2579,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>301</v>
       </c>
@@ -2587,7 +2590,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>302</v>
       </c>
@@ -2598,7 +2601,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>302</v>
       </c>
@@ -2609,7 +2612,7 @@
         <v>18.8</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>303</v>
       </c>
@@ -2620,7 +2623,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>303</v>
       </c>
@@ -2631,7 +2634,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>304</v>
       </c>
@@ -2642,7 +2645,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>305</v>
       </c>
@@ -2653,7 +2656,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>306</v>
       </c>
@@ -2664,7 +2667,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>307</v>
       </c>
@@ -2675,7 +2678,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>308</v>
       </c>
@@ -2686,7 +2689,7 @@
         <v>18.7</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>309</v>
       </c>
@@ -2697,7 +2700,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>310</v>
       </c>
@@ -2708,7 +2711,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>311</v>
       </c>
@@ -2719,7 +2722,7 @@
         <v>19.2</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>312</v>
       </c>
@@ -2730,7 +2733,7 @@
         <v>19.7</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>313</v>
       </c>
@@ -2741,7 +2744,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>314</v>
       </c>
@@ -2752,7 +2755,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>315</v>
       </c>
@@ -2763,7 +2766,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>316</v>
       </c>
@@ -2785,9 +2788,9 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C45"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>274</v>
       </c>
@@ -2798,7 +2801,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>277</v>
       </c>
@@ -2809,7 +2812,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>278</v>
       </c>
@@ -2820,7 +2823,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>279</v>
       </c>
@@ -2831,7 +2834,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>280</v>
       </c>
@@ -2842,7 +2845,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>281</v>
       </c>
@@ -2853,7 +2856,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>282</v>
       </c>
@@ -2864,7 +2867,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>283</v>
       </c>
@@ -2875,7 +2878,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>284</v>
       </c>
@@ -2886,7 +2889,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>285</v>
       </c>
@@ -2897,7 +2900,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>286</v>
       </c>
@@ -2908,7 +2911,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>287</v>
       </c>
@@ -2919,7 +2922,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>288</v>
       </c>
@@ -2930,7 +2933,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>288</v>
       </c>
@@ -2941,7 +2944,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>289</v>
       </c>
@@ -2952,7 +2955,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>290</v>
       </c>
@@ -2963,7 +2966,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>291</v>
       </c>
@@ -2974,7 +2977,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>292</v>
       </c>
@@ -2985,7 +2988,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>293</v>
       </c>
@@ -2996,7 +2999,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>294</v>
       </c>
@@ -3007,7 +3010,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>295</v>
       </c>
@@ -3018,7 +3021,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>296</v>
       </c>
@@ -3029,7 +3032,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>297</v>
       </c>
@@ -3040,7 +3043,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>298</v>
       </c>
@@ -3051,7 +3054,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>299</v>
       </c>
@@ -3062,7 +3065,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>300</v>
       </c>
@@ -3073,7 +3076,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>301</v>
       </c>
@@ -3084,7 +3087,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>301</v>
       </c>
@@ -3095,7 +3098,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>302</v>
       </c>
@@ -3106,7 +3109,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>302</v>
       </c>
@@ -3117,7 +3120,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>303</v>
       </c>
@@ -3128,7 +3131,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>303</v>
       </c>
@@ -3139,7 +3142,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>304</v>
       </c>
@@ -3150,7 +3153,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>305</v>
       </c>
@@ -3161,7 +3164,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>306</v>
       </c>
@@ -3172,7 +3175,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>307</v>
       </c>
@@ -3183,7 +3186,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>308</v>
       </c>
@@ -3194,7 +3197,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>309</v>
       </c>
@@ -3205,7 +3208,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>310</v>
       </c>
@@ -3216,7 +3219,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>311</v>
       </c>
@@ -3227,7 +3230,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>312</v>
       </c>
@@ -3238,7 +3241,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>313</v>
       </c>
@@ -3249,7 +3252,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>314</v>
       </c>
@@ -3260,7 +3263,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>315</v>
       </c>
@@ -3271,7 +3274,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>316</v>
       </c>
@@ -3293,9 +3296,9 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:G1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>274</v>
       </c>
@@ -3329,9 +3332,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:CO2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:93" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:93" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -3612,7 +3615,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="2" spans="1:93" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:93" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9848</v>
       </c>
@@ -3883,9 +3886,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Q12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>142</v>
       </c>
@@ -3938,7 +3941,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9848</v>
       </c>
@@ -3967,7 +3970,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9848</v>
       </c>
@@ -4002,7 +4005,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9848</v>
       </c>
@@ -4031,7 +4034,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9848</v>
       </c>
@@ -4081,7 +4084,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9848</v>
       </c>
@@ -4131,7 +4134,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9848</v>
       </c>
@@ -4166,7 +4169,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9848</v>
       </c>
@@ -4213,7 +4216,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9848</v>
       </c>
@@ -4242,7 +4245,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9848</v>
       </c>
@@ -4277,7 +4280,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9848</v>
       </c>
@@ -4312,7 +4315,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9848</v>
       </c>
@@ -4358,9 +4361,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>142</v>
       </c>
@@ -4392,7 +4395,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9848</v>
       </c>
@@ -4424,7 +4427,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9848</v>
       </c>
@@ -4456,7 +4459,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9848</v>
       </c>
@@ -4499,7 +4502,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -4511,9 +4514,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>142</v>
       </c>
@@ -4545,7 +4548,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9848</v>
       </c>
@@ -4588,9 +4591,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>142</v>
       </c>
@@ -4607,7 +4610,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9848</v>
       </c>
@@ -4629,7 +4632,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -4641,9 +4644,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:P36"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>142</v>
       </c>
@@ -4693,7 +4696,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9848</v>
       </c>
@@ -4743,7 +4746,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9848</v>
       </c>
@@ -4793,7 +4796,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9848</v>
       </c>
@@ -4843,7 +4846,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9848</v>
       </c>
@@ -4893,7 +4896,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9848</v>
       </c>
@@ -4943,7 +4946,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9848</v>
       </c>
@@ -4993,7 +4996,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9848</v>
       </c>
@@ -5043,7 +5046,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9848</v>
       </c>
@@ -5093,7 +5096,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9848</v>
       </c>
@@ -5143,7 +5146,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9848</v>
       </c>
@@ -5193,7 +5196,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9848</v>
       </c>
@@ -5243,7 +5246,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9848</v>
       </c>
@@ -5293,7 +5296,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>9848</v>
       </c>
@@ -5343,7 +5346,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>9848</v>
       </c>
@@ -5393,7 +5396,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>9848</v>
       </c>
@@ -5443,7 +5446,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>9848</v>
       </c>
@@ -5493,7 +5496,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>9848</v>
       </c>
@@ -5543,7 +5546,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>9848</v>
       </c>
@@ -5593,7 +5596,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>9848</v>
       </c>
@@ -5643,7 +5646,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>9848</v>
       </c>
@@ -5693,7 +5696,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>9848</v>
       </c>
@@ -5743,7 +5746,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>9848</v>
       </c>
@@ -5793,7 +5796,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>9848</v>
       </c>
@@ -5843,7 +5846,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>9848</v>
       </c>
@@ -5893,7 +5896,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>9848</v>
       </c>
@@ -5943,7 +5946,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>9848</v>
       </c>
@@ -5972,7 +5975,7 @@
         <v>233</v>
       </c>
       <c r="J27" t="s">
-        <v>234</v>
+        <v>320</v>
       </c>
       <c r="K27" t="s">
         <v>235</v>
@@ -5993,7 +5996,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>9848</v>
       </c>
@@ -6022,7 +6025,7 @@
         <v>233</v>
       </c>
       <c r="J28" t="s">
-        <v>234</v>
+        <v>320</v>
       </c>
       <c r="K28" t="s">
         <v>249</v>
@@ -6043,7 +6046,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>9848</v>
       </c>
@@ -6072,7 +6075,7 @@
         <v>233</v>
       </c>
       <c r="J29" t="s">
-        <v>234</v>
+        <v>320</v>
       </c>
       <c r="K29" t="s">
         <v>251</v>
@@ -6093,7 +6096,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>9848</v>
       </c>
@@ -6122,7 +6125,7 @@
         <v>233</v>
       </c>
       <c r="J30" t="s">
-        <v>234</v>
+        <v>320</v>
       </c>
       <c r="K30" t="s">
         <v>245</v>
@@ -6143,7 +6146,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>9848</v>
       </c>
@@ -6172,7 +6175,7 @@
         <v>233</v>
       </c>
       <c r="J31" t="s">
-        <v>234</v>
+        <v>320</v>
       </c>
       <c r="K31" t="s">
         <v>254</v>
@@ -6193,7 +6196,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>9848</v>
       </c>
@@ -6222,7 +6225,7 @@
         <v>233</v>
       </c>
       <c r="J32" t="s">
-        <v>234</v>
+        <v>320</v>
       </c>
       <c r="K32" t="s">
         <v>264</v>
@@ -6243,7 +6246,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>9848</v>
       </c>
@@ -6272,7 +6275,7 @@
         <v>233</v>
       </c>
       <c r="J33" t="s">
-        <v>234</v>
+        <v>320</v>
       </c>
       <c r="K33" t="s">
         <v>256</v>
@@ -6293,7 +6296,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>9848</v>
       </c>
@@ -6322,7 +6325,7 @@
         <v>233</v>
       </c>
       <c r="J34" t="s">
-        <v>234</v>
+        <v>320</v>
       </c>
       <c r="K34" t="s">
         <v>229</v>
@@ -6343,7 +6346,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>9848</v>
       </c>
@@ -6372,7 +6375,7 @@
         <v>233</v>
       </c>
       <c r="J35" t="s">
-        <v>234</v>
+        <v>320</v>
       </c>
       <c r="K35" t="s">
         <v>240</v>
@@ -6393,7 +6396,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>9848</v>
       </c>
@@ -6422,7 +6425,7 @@
         <v>233</v>
       </c>
       <c r="J36" t="s">
-        <v>234</v>
+        <v>320</v>
       </c>
       <c r="K36" t="s">
         <v>242</v>
@@ -6446,7 +6449,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:P8 A16:P36 A9:D9 F9:P9 A10:D15 F10:P15" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:P8 A16:P26 A9:D9 F9:P9 A10:D15 F10:P15 A27:I36 K27:P36" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>